--- a/AAII_Financials/Quarterly/KSS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KSS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>KSS</t>
   </si>
@@ -656,503 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43771</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43680</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43589</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43498</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43407</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43316</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43134</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3515000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3167000</v>
+      </c>
+      <c r="F8" s="3">
         <v>5173000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3575000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3546000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3233000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5397000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3710000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3732000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3382000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5956000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4054000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3895000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3571000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>6019000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4277000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4087000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3715000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>6499000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4600000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4447000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3887000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6141000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3979000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3407000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2428000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>6832000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>4625000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4430000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>4087000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>6823000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>4628000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4570000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>4208000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>7057000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>4567000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>4395000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>4065000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>6205000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>4327000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1993000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1802000</v>
+      </c>
+      <c r="F9" s="3">
         <v>3324000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2059000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2011000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1834000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3473000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2137000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2128000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1923000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3860000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2349000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2242000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2047000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4444000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2541000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2332000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2140000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4155000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2623000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2426000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2233000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>4000000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2424000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2149000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1600000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>4400000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2775000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2550000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2415000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>4345000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2752000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>2605000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>2496000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>4496000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2727000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>2525000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>2428000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>4132000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>2720000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1522000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1365000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1849000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1516000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1535000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1399000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1924000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1573000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1604000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1459000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2096000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1705000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1653000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1524000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1575000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1736000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1755000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1575000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>2344000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1977000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2021000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1654000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2141000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1555000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1258000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>828000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2432000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1850000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1880000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1672000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2478000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1876000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1965000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1712000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>2561000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1840000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1870000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1637000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>2073000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>1607000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1218,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1313,8 +1339,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,32 +1464,38 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-118000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>76000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1473,11 +1511,11 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1495,50 +1533,50 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>201000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>36000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>50000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>25000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>293000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>58000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>7000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>49000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>125000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
@@ -1549,129 +1587,141 @@
         <v>0</v>
       </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E15" s="3">
         <v>174000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>174000</v>
+      </c>
+      <c r="G15" s="3">
         <v>176000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>175000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>175000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>183000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>184000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>188000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>188000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>187000</v>
       </c>
       <c r="M15" s="3">
         <v>188000</v>
       </c>
       <c r="N15" s="3">
-        <v>186000</v>
+        <v>187000</v>
       </c>
       <c r="O15" s="3">
         <v>188000</v>
       </c>
       <c r="P15" s="3">
+        <v>186000</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>188000</v>
+      </c>
+      <c r="R15" s="3">
         <v>200000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>202000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>206000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>200000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>207000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>210000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>210000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>211000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>218000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>210000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>219000</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>227000</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>230000</v>
       </c>
       <c r="AC15" s="3">
         <v>227000</v>
       </c>
       <c r="AD15" s="3">
+        <v>230000</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>227000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>228000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>230000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>239000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>243000</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>241000</v>
       </c>
       <c r="AI15" s="3">
         <v>243000</v>
       </c>
       <c r="AJ15" s="3">
-        <v>267000</v>
+        <v>241000</v>
       </c>
       <c r="AK15" s="3">
         <v>243000</v>
       </c>
       <c r="AL15" s="3">
+        <v>267000</v>
+      </c>
+      <c r="AM15" s="3">
         <v>243000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
+        <v>243000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>238000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>238000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AQ15" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1760,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3354000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3121000</v>
+      </c>
+      <c r="F17" s="3">
         <v>4961000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3498000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3385000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3173000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5195000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3612000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3566000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3339000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5657000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3897000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3732000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3473000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6321000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4077000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3821000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3633000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>6049000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4213000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3877000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3815000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5825000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3957000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3289000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3146000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6431000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4412000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>4054000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3969000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>6403000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>4370000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>4118000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>4040000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>6490000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>4310000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>3988000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>3880000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>5731000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>4026000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F18" s="3">
         <v>212000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>77000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>161000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>60000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>202000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>98000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>166000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>43000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>299000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>157000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>163000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>98000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-302000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>200000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>266000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>82000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>450000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>387000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>570000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>72000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>316000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>22000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>118000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-718000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>401000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>213000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>376000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>118000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>420000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>258000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>452000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>168000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>567000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>257000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>407000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>185000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>474000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>301000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,8 +2055,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,77 +2098,77 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-45000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-41000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-36000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-35000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-37000</v>
       </c>
       <c r="V20" s="3">
         <v>-35000</v>
       </c>
       <c r="W20" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-67000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-78000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-78000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-59000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-63000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-65000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-71000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-74000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-74000</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>-75000</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>-76000</v>
       </c>
       <c r="AN20" s="3">
         <v>-75000</v>
@@ -2110,193 +2176,205 @@
       <c r="AO20" s="3">
         <v>-76000</v>
       </c>
+      <c r="AP20" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AQ20" s="3">
+        <v>-76000</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>220000</v>
+      </c>
+      <c r="F21" s="3">
         <v>386000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>253000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>336000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>235000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>385000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>282000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>354000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>231000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>486000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>345000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>349000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>286000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-144000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>357000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>431000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>246000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>622000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>560000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>745000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>216000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>464000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>154000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>259000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-549000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>615000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>424000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>584000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>329000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>600000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>437000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>627000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>340000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>760000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>425000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>576000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>347000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>637000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>457000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F22" s="3">
         <v>59000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>75000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>78000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>76000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>74000</v>
       </c>
       <c r="I22" s="3">
         <v>76000</v>
       </c>
       <c r="J22" s="3">
+        <v>74000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L22" s="3">
         <v>86000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>83000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>82000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>89000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>89000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>84000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>36000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>36000</v>
       </c>
       <c r="R22" s="3">
         <v>36000</v>
       </c>
       <c r="S22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="T22" s="3">
+        <v>36000</v>
+      </c>
+      <c r="U22" s="3">
         <v>32000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>30000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>29000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>27000</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2306,35 +2384,35 @@
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>34000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>34000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>33000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>33000</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL22" s="3">
         <v>0</v>
@@ -2348,246 +2426,264 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="F23" s="3">
         <v>153000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>201000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-16000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>52000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>22000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>80000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-40000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>217000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>68000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>74000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>14000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-380000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>119000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>189000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>14000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>385000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>321000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>508000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>5000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>246000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-56000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>40000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-776000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>351000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>161000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>323000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>66000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>361000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>195000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>387000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>97000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>493000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>183000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>332000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>109000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>399000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>225000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F24" s="3">
         <v>28000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-10000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>48000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>14000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-13000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>31000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>16000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>22000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>46000</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>86000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>78000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>126000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-9000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-44000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-235000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>86000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>38000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>82000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>4000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>89000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>34000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>95000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>22000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>161000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>66000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>124000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>43000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>146000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2801,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F26" s="3">
         <v>125000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>8000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>153000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-15000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>48000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>22000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>66000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-27000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>186000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>59000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>58000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>14000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>97000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>143000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>14000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>299000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>243000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>382000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>14000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>343000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>47000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-541000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>265000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>123000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>241000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>62000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>272000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>161000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>292000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>332000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>117000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>208000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>66000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>253000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F27" s="3">
         <v>125000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>153000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>48000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>22000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>66000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-27000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>186000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>59000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>58000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>14000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>97000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>143000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>14000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>299000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>243000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>382000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>14000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>343000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>47000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-541000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>265000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>123000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>241000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>62000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>272000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>161000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>292000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>332000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>117000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>208000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>66000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>253000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3176,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,33 +3265,33 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>136000</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3181,8 +3301,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3426,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,8 +3551,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3460,77 +3598,77 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>42000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>45000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>41000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>36000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>35000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>37000</v>
       </c>
       <c r="V32" s="3">
         <v>35000</v>
       </c>
       <c r="W32" s="3">
+        <v>37000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>67000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>70000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>78000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>78000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>58000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>16000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>18000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>20000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>19000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>59000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>63000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>65000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>71000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>74000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>74000</v>
-      </c>
-      <c r="AL32" s="3">
-        <v>75000</v>
-      </c>
-      <c r="AM32" s="3">
-        <v>76000</v>
       </c>
       <c r="AN32" s="3">
         <v>75000</v>
@@ -3538,127 +3676,139 @@
       <c r="AO32" s="3">
         <v>76000</v>
       </c>
+      <c r="AP32" s="3">
+        <v>75000</v>
+      </c>
+      <c r="AQ32" s="3">
+        <v>76000</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F33" s="3">
         <v>125000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>153000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>48000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>22000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>66000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>186000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>59000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>58000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>14000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>97000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>143000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>14000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>299000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>243000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>382000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>14000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>343000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>47000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-541000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>265000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>123000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>241000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>62000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>272000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>161000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>292000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>468000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>117000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>208000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>66000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>253000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3926,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F35" s="3">
         <v>125000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>153000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>48000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>22000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>66000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>186000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>59000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>58000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>14000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>97000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>143000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>14000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>299000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>243000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>382000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>14000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>343000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>47000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-541000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>265000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>123000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>241000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>62000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>272000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>161000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>292000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>468000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>117000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>208000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>66000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>253000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43771</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43680</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43589</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43498</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43407</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43316</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43134</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4230,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,127 +4275,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>821000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>429000</v>
+      </c>
+      <c r="F41" s="3">
         <v>674000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>144000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>174000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>153000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>134000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>174000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>231000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>228000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>183000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>190000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>204000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>286000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>153000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>194000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>222000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>646000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1587000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1873000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2569000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1609000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2271000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1939000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2428000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2039000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>723000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>490000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>625000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>543000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>934000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1047000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>1066000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>822000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>1308000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>736000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>552000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>625000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>1074000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>597000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4343,52 +4521,58 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>125000</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>159000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>167000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4405,27 +4589,27 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z43" s="3">
         <v>610000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>115000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>205000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>174000</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4438,11 +4622,11 @@
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="3">
-        <v>0</v>
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ43" s="3">
         <v>0</v>
@@ -4462,365 +4646,389 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2913000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2897000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2745000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3895000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2994000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3137000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2945000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>4099000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3151000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3083000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2880000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>4239000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3474000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3526000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>3189000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>4874000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>4034000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>3736000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>3067000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>3642000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2733000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2667000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>2590000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>3607000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>2698000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>3557000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3537000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>4887000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3656000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3680000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>3475000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>4844000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>3572000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>3726000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>3542000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>4632000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>3853000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>3991000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>3795000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>4721000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>326000</v>
+      </c>
+      <c r="F45" s="3">
         <v>11000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>269000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>306000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>290000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>11000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>344000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>331000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>345000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>14000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>291000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>296000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>347000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>394000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>366000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>374000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>381000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>369000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>373000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>356000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>919000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>364000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>335000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>357000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>400000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>389000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>404000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>397000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>412000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>426000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>446000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>404000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>435000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>530000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>332000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>381000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>328000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>378000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>336000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4019000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3652000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3691000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4308000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3474000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3580000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3388000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4617000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3713000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3656000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3410000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4720000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3974000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4159000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3736000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5434000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4630000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4763000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5023000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>5888000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>5658000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>5195000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>5835000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>5996000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5688000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>6170000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4649000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>5781000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>4678000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>4635000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>4835000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>6337000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>5042000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>4983000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>5380000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>5700000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>4786000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>4944000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>5247000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>5654000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4860,11 +5068,11 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4881,18 +5089,18 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3">
         <v>232000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4905,11 +5113,11 @@
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG47" s="3">
         <v>0</v>
@@ -4938,127 +5146,139 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8958000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9097000</v>
+      </c>
+      <c r="F48" s="3">
         <v>9252000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>9382000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>9476000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9583000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9691000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9972000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>10009000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>10162000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>10219000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>10353000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>10438000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>10171000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>10230000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>10435000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>10524000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>10014000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>9552000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>9622000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>9408000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>9045000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>9087000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>9298000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>9388000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>9542000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>9743000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>9791000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>9704000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>9664000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>7428000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>7538000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>7635000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>7694000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>7773000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>7974000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>8068000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>8069000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>8103000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>8203000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5176,8 +5396,14 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5521,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5646,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>433000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>416000</v>
+      </c>
+      <c r="F52" s="3">
         <v>387000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>454000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>441000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>476000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>442000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>465000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>458000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>460000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>348000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>394000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>382000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>380000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>379000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>365000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>469000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>476000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>479000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>441000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>440000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>449000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>183000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>150000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>159000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>157000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>163000</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>167000</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>160000</v>
       </c>
       <c r="AE52" s="3">
         <v>167000</v>
       </c>
       <c r="AF52" s="3">
+        <v>160000</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>167000</v>
+      </c>
+      <c r="AH52" s="3">
         <v>206000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>243000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>238000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>239000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>236000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>226000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>230000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>231000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>224000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>219000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5896,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13410000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13165000</v>
+      </c>
+      <c r="F54" s="3">
         <v>13362000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>14144000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13391000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>13639000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>13559000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>15054000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>14180000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>14278000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>14009000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>15467000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14794000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>14710000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>14345000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16234000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>15623000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>15253000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>15054000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15951000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>15506000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>14689000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>15337000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>15444000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>15235000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>15869000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>14555000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>15739000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>14542000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>14466000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>12469000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>14118000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>12915000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>12916000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>13389000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>13900000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>13084000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>13244000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>13574000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>14076000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +6070,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,722 +6115,760 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1418000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1248000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1171000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1842000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1134000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1026000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1042000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1873000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1317000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1220000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1134000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1918000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1376000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1310000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1330000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2014000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1497000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1679000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1683000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2135000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1495000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1378000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1476000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2184000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1064000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1866000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1206000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2454000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1330000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1295000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1187000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2583000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>1404000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>1454000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>1271000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>2113000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>1370000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>1480000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>1507000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>2097000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>184000</v>
+      </c>
+      <c r="F58" s="3">
         <v>179000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>225000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>255000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1077000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>826000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1275000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>936000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>528000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>277000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>914000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>848000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1080000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>454000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>927000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>339000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>272000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>118000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>117000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>117000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>112000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>115000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>127000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>126000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>124000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>124000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>110000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>119000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>115000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>115000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>121000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>122000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>123000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>126000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>131000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>133000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>134000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>131000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>128000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>359000</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>466000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>367000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>1331000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1545000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1534000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1443000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1485000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1687000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1697000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1448000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1431000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1432000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1376000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1297000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1439000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1511000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1391000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1382000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1428000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1303000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1244000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1253000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>1312000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>1261000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>1168000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>1225000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>1336000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>1301000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2696000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2465000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2531000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3307000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2548000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3280000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3131000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4393000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3438000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3013000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2612000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4156000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3470000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3554000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3115000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4486000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3370000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3394000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>3286000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3939000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3309000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2938000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3022000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3743000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2566000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3287000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2769000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>4075000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2840000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2792000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2730000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>4007000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>2770000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>2830000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>2709000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>3505000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>2671000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>2839000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>2974000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>3526000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6233000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6349000</v>
+      </c>
+      <c r="F61" s="3">
         <v>6451000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6577000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6601000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6294000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6333000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6506000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6542000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7072000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7099000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7132000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7144000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6981000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4423000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4538000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>4577000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>4330000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>4043000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3981000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3815000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3382000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>3838000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3852000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4806000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>4800000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>3223000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>3188000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>3125000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>3080000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>3384000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>3800000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>3810000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>3864000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>4388000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>4418000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>4433000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>4452000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>4480000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>4496000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>239000</v>
+      </c>
+      <c r="F62" s="3">
         <v>241000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>254000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>261000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>259000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>265000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>273000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>275000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>286000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>298000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>321000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>324000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>326000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3044000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3114000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3132000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3073000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3064000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3100000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3163000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3252000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3281000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3011000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3026000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2992000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>3113000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>3121000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>3122000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>3152000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>828000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>858000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>848000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>866000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>873000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>948000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>959000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>959000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>943000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>947000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6986,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +7111,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7236,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9242000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9141000</v>
+      </c>
+      <c r="F66" s="3">
         <v>9314000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>10214000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>9464000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9860000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9757000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11250000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>10350000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10465000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10116000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>11716000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>11059000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10990000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10582000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12138000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>11079000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>10797000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10393000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>11020000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>10287000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9572000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10141000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>10606000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>10398000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>11079000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>9105000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>10384000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>9087000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>9024000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>6942000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>8665000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>7428000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>7560000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>7970000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>8871000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>8063000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>8250000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>8397000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>8969000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7410,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7531,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7656,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7781,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7906,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1195000</v>
+      </c>
+      <c r="F72" s="3">
         <v>1223000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1113000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1119000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>979000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1008000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2828000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2861000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2851000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2934000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2803000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2800000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2798000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>13995000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>14324000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>14285000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>14207000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>14257000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>13991000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>13786000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>13443000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>13468000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>13125000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>13137000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>13090000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>13745000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>13585000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>13568000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>13436000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>13395000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>13224000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>13163000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>12972000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>12999000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>12631000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>12599000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>12493000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>12522000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>12358000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +8156,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8281,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8406,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4168000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4024000</v>
+      </c>
+      <c r="F76" s="3">
         <v>4048000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3930000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3927000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3779000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3802000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3804000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3830000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3813000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3893000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3751000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3735000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3720000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3763000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4096000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4544000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4456000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4661000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4931000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5219000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>5117000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5196000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4838000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4837000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4790000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>5450000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>5355000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>5455000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>5442000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>5527000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>5453000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>5487000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>5356000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>5419000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>5029000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>5021000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>4994000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>5177000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>5107000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8656,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43771</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43680</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43589</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43498</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43407</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43316</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43134</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="F81" s="3">
         <v>125000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>153000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>48000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>22000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>66000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>186000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>59000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>58000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>14000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>97000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>143000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>14000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>299000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>243000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>382000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>14000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>343000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>47000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-541000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>265000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>123000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>241000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>62000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>272000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>161000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>292000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>468000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>117000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>208000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>66000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>253000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>146000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8960,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>175000</v>
+      </c>
+      <c r="F83" s="3">
         <v>183000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>184000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>188000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>188000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>187000</v>
       </c>
       <c r="I83" s="3">
         <v>188000</v>
       </c>
       <c r="J83" s="3">
-        <v>186000</v>
+        <v>187000</v>
       </c>
       <c r="K83" s="3">
         <v>188000</v>
       </c>
       <c r="L83" s="3">
+        <v>186000</v>
+      </c>
+      <c r="M83" s="3">
+        <v>188000</v>
+      </c>
+      <c r="N83" s="3">
         <v>200000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>202000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>206000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>200000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>200000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>202000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>206000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>200000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>207000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>210000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>210000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>211000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>218000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>210000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>219000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>227000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>230000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>229000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>228000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>230000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>239000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>242000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>240000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>243000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>267000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>242000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>244000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>238000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>238000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9206,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9331,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9456,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9581,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9706,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="F89" s="3">
         <v>750000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>124000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>598000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-92000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>596000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-195000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>254000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-7000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>789000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>151000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>430000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-202000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>707000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>121000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-86000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-460000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>497000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>82000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1414000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>278000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>428000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>606000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>251000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>53000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>612000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>369000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>540000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>136000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>684000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>376000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>660000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>387000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>822000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>493000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>330000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>46000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>869000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>438000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9880,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-64000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-108000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-90000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-110000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-99000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-128000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-113000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-126000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-82000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-157000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-244000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-94000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-185000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-327000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-221000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-179000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-235000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-132000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-59000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-68000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-162000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-239000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-201000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-238000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-146000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-179000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-133000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-148000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-183000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-216000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-354000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-842000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +10126,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10251,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-64000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-90000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-71000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-108000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-104000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-126000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-111000</v>
       </c>
       <c r="K94" s="3">
         <v>-126000</v>
       </c>
       <c r="L94" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-126000</v>
+      </c>
+      <c r="N94" s="3">
         <v>-71000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-156000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-241000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-94000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-158000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-327000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-217000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-179000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-204000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-130000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-57000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>159000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-162000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-167000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-231000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-201000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-238000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-120000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-146000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-173000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-133000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-120000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-146000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-180000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-203000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-172000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-247000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,8 +10425,10 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9979,10 +10445,10 @@
         <v>14000</v>
       </c>
       <c r="H96" s="3">
-        <v>56000</v>
+        <v>14000</v>
       </c>
       <c r="I96" s="3">
-        <v>55000</v>
+        <v>14000</v>
       </c>
       <c r="J96" s="3">
         <v>56000</v>
@@ -9991,7 +10457,7 @@
         <v>55000</v>
       </c>
       <c r="L96" s="3">
-        <v>55000</v>
+        <v>56000</v>
       </c>
       <c r="M96" s="3">
         <v>55000</v>
@@ -10003,85 +10469,91 @@
         <v>55000</v>
       </c>
       <c r="P96" s="3">
+        <v>55000</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>55000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-57000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-64000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-63000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-33000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-37000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-38000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-39000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-108000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-104000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-105000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-106000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-108000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-99000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-99000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-101000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-101000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-91000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-91000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-92000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-94000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-88000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-88000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10671,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10796,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,127 +10921,139 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-87000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-156000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-64000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-506000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>219000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-532000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>264000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-140000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>178000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-725000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-271000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>429000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-667000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>9000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-11000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-264000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-604000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-574000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-324000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-883000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1028000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1425000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-212000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-273000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-257000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-677000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-249000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-243000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-740000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-130000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-163000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-223000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-292000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-219000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-290000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,11 +11093,11 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10675,123 +11171,135 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-245000</v>
+      </c>
+      <c r="F102" s="3">
         <v>530000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-30000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>21000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>19000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-40000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-57000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>45000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-14000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-82000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>133000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-28000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-424000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-941000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-286000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-696000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>960000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-662000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>332000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-489000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>389000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1316000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>233000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>82000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-391000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-113000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>244000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-486000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>572000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>184000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>-449000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>477000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>-103000</v>
       </c>
     </row>
